--- a/branches/feat/crmi-artifact-metadata/ValueSet-mii-vs-molgen-familiaere-linie.xlsx
+++ b/branches/feat/crmi-artifact-metadata/ValueSet-mii-vs-molgen-familiaere-linie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:09:33+00:00</t>
+    <t>2026-09-11T10:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
